--- a/crates/xlstream-eval/tests/fixtures/info/type_checks.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/info/type_checks.xlsx
@@ -9,7 +9,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Lookup1" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,99 +20,84 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
-  <si>
-    <t xml:space="preserve">num</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+  <si>
+    <t xml:space="preserve">number</t>
   </si>
   <si>
     <t xml:space="preserve">text</t>
   </si>
   <si>
-    <t xml:space="preserve">flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">isnumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">istext</t>
-  </si>
-  <si>
-    <t xml:space="preserve">islogical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">isnontext</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iserror</t>
-  </si>
-  <si>
-    <t xml:space="preserve">isna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">na</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type</t>
+    <t xml:space="preserve">bool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">empty_col</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isblank_num</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isblank_empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isnumber_num</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isnumber_text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">istext_text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">istext_num</t>
+  </si>
+  <si>
+    <t xml:space="preserve">islogical_bool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">islogical_num</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isnontext_num</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isnontext_text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iserror_div0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iserror_ok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type_num</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type_text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type_bool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">na_func</t>
   </si>
   <si>
     <t xml:space="preserve">hello</t>
   </si>
   <si>
-    <t xml:space="preserve">WORLD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  spaces  here  </t>
+    <t xml:space="preserve">world</t>
   </si>
   <si>
     <t xml:space="preserve">abc</t>
   </si>
   <si>
-    <t xml:space="preserve">short</t>
-  </si>
-  <si>
     <t xml:space="preserve">test</t>
   </si>
   <si>
-    <t xml:space="preserve">ProPer Case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">num123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foo bar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Americas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LATAM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LatAm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MidEast</t>
+    <t xml:space="preserve">foo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bar</t>
   </si>
 </sst>
 </file>
@@ -390,7 +374,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -427,137 +411,260 @@
       <c r="K1" s="0" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="0" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="b">
+      <c r="E2" s="1" t="b">
+        <f aca="false">ISBLANK(A2)</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="b">
+        <f aca="false">ISBLANK(D2)</f>
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="b">
         <f aca="false">ISNUMBER(A2)</f>
         <v>1</v>
       </c>
-      <c r="E2" s="1" t="b">
+      <c r="H2" s="1" t="b">
+        <f aca="false">ISNUMBER(B2)</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="1" t="b">
         <f aca="false">ISTEXT(B2)</f>
         <v>1</v>
       </c>
-      <c r="F2" s="1" t="b">
+      <c r="J2" s="1" t="b">
+        <f aca="false">ISTEXT(A2)</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="1" t="b">
         <f aca="false">ISLOGICAL(C2)</f>
         <v>1</v>
       </c>
-      <c r="G2" s="1" t="b">
+      <c r="L2" s="1" t="b">
+        <f aca="false">ISLOGICAL(A2)</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="1" t="b">
         <f aca="false">ISNONTEXT(A2)</f>
         <v>1</v>
       </c>
-      <c r="H2" s="1" t="b">
+      <c r="N2" s="1" t="b">
+        <f aca="false">ISNONTEXT(B2)</f>
+        <v>0</v>
+      </c>
+      <c r="O2" s="1" t="b">
         <f aca="false">ISERROR(1/0)</f>
         <v>1</v>
       </c>
-      <c r="I2" s="1" t="b">
-        <f aca="false">ISNA(VLOOKUP("ZZZ",Lookup1!A:C,2,FALSE()))</f>
-        <v>1</v>
-      </c>
-      <c r="J2" s="0" t="e">
+      <c r="P2" s="1" t="b">
+        <f aca="false">ISERROR(A2)</f>
+        <v>0</v>
+      </c>
+      <c r="Q2" s="0" t="n">
+        <f aca="false">TYPE(A2)</f>
+        <v>1</v>
+      </c>
+      <c r="R2" s="0" t="n">
+        <f aca="false">TYPE(B2)</f>
+        <v>2</v>
+      </c>
+      <c r="S2" s="0" t="n">
+        <f aca="false">TYPE(C2)</f>
+        <v>8</v>
+      </c>
+      <c r="T2" s="0" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
-      </c>
-      <c r="K2" s="0" t="n">
-        <f aca="false">TYPE(A2)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="D3" s="1" t="b">
+      <c r="E3" s="1" t="b">
+        <f aca="false">ISBLANK(A3)</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="b">
+        <f aca="false">ISBLANK(D3)</f>
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="b">
         <f aca="false">ISNUMBER(A3)</f>
         <v>1</v>
       </c>
-      <c r="E3" s="1" t="b">
+      <c r="H3" s="1" t="b">
+        <f aca="false">ISNUMBER(B3)</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="1" t="b">
         <f aca="false">ISTEXT(B3)</f>
         <v>1</v>
       </c>
-      <c r="F3" s="1" t="b">
+      <c r="J3" s="1" t="b">
+        <f aca="false">ISTEXT(A3)</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="1" t="b">
         <f aca="false">ISLOGICAL(C3)</f>
         <v>1</v>
       </c>
-      <c r="G3" s="1" t="b">
+      <c r="L3" s="1" t="b">
+        <f aca="false">ISLOGICAL(A3)</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="1" t="b">
         <f aca="false">ISNONTEXT(A3)</f>
         <v>1</v>
       </c>
-      <c r="H3" s="1" t="b">
+      <c r="N3" s="1" t="b">
+        <f aca="false">ISNONTEXT(B3)</f>
+        <v>0</v>
+      </c>
+      <c r="O3" s="1" t="b">
         <f aca="false">ISERROR(1/0)</f>
         <v>1</v>
       </c>
-      <c r="I3" s="1" t="b">
-        <f aca="false">ISNA(VLOOKUP("ZZZ",Lookup1!A:C,2,FALSE()))</f>
-        <v>1</v>
-      </c>
-      <c r="J3" s="0" t="e">
+      <c r="P3" s="1" t="b">
+        <f aca="false">ISERROR(A3)</f>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="0" t="n">
+        <f aca="false">TYPE(A3)</f>
+        <v>1</v>
+      </c>
+      <c r="R3" s="0" t="n">
+        <f aca="false">TYPE(B3)</f>
+        <v>2</v>
+      </c>
+      <c r="S3" s="0" t="n">
+        <f aca="false">TYPE(C3)</f>
+        <v>8</v>
+      </c>
+      <c r="T3" s="0" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
-      </c>
-      <c r="K3" s="0" t="n">
-        <f aca="false">TYPE(A3)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
-        <v>0</v>
+        <v>-7.5</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D4" s="1" t="b">
+      <c r="E4" s="1" t="b">
+        <f aca="false">ISBLANK(A4)</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="b">
+        <f aca="false">ISBLANK(D4)</f>
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="b">
         <f aca="false">ISNUMBER(A4)</f>
         <v>1</v>
       </c>
-      <c r="E4" s="1" t="b">
+      <c r="H4" s="1" t="b">
+        <f aca="false">ISNUMBER(B4)</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="1" t="b">
         <f aca="false">ISTEXT(B4)</f>
         <v>1</v>
       </c>
-      <c r="F4" s="1" t="b">
+      <c r="J4" s="1" t="b">
+        <f aca="false">ISTEXT(A4)</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="b">
         <f aca="false">ISLOGICAL(C4)</f>
         <v>1</v>
       </c>
-      <c r="G4" s="1" t="b">
+      <c r="L4" s="1" t="b">
+        <f aca="false">ISLOGICAL(A4)</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="1" t="b">
         <f aca="false">ISNONTEXT(A4)</f>
         <v>1</v>
       </c>
-      <c r="H4" s="1" t="b">
+      <c r="N4" s="1" t="b">
+        <f aca="false">ISNONTEXT(B4)</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="1" t="b">
         <f aca="false">ISERROR(1/0)</f>
         <v>1</v>
       </c>
-      <c r="I4" s="1" t="b">
-        <f aca="false">ISNA(VLOOKUP("ZZZ",Lookup1!A:C,2,FALSE()))</f>
-        <v>1</v>
-      </c>
-      <c r="J4" s="0" t="e">
+      <c r="P4" s="1" t="b">
+        <f aca="false">ISERROR(A4)</f>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="0" t="n">
+        <f aca="false">TYPE(A4)</f>
+        <v>1</v>
+      </c>
+      <c r="R4" s="0" t="n">
+        <f aca="false">TYPE(B4)</f>
+        <v>2</v>
+      </c>
+      <c r="S4" s="0" t="n">
+        <f aca="false">TYPE(C4)</f>
+        <v>8</v>
+      </c>
+      <c r="T4" s="0" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
-      </c>
-      <c r="K4" s="0" t="n">
-        <f aca="false">TYPE(A4)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -565,381 +672,227 @@
         <v>100</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D5" s="1" t="b">
+      <c r="E5" s="1" t="b">
+        <f aca="false">ISBLANK(A5)</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="b">
+        <f aca="false">ISBLANK(D5)</f>
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="b">
         <f aca="false">ISNUMBER(A5)</f>
         <v>1</v>
       </c>
-      <c r="E5" s="1" t="b">
+      <c r="H5" s="1" t="b">
+        <f aca="false">ISNUMBER(B5)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="b">
         <f aca="false">ISTEXT(B5)</f>
         <v>1</v>
       </c>
-      <c r="F5" s="1" t="b">
+      <c r="J5" s="1" t="b">
+        <f aca="false">ISTEXT(A5)</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="b">
         <f aca="false">ISLOGICAL(C5)</f>
         <v>1</v>
       </c>
-      <c r="G5" s="1" t="b">
+      <c r="L5" s="1" t="b">
+        <f aca="false">ISLOGICAL(A5)</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="1" t="b">
         <f aca="false">ISNONTEXT(A5)</f>
         <v>1</v>
       </c>
-      <c r="H5" s="1" t="b">
+      <c r="N5" s="1" t="b">
+        <f aca="false">ISNONTEXT(B5)</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="1" t="b">
         <f aca="false">ISERROR(1/0)</f>
         <v>1</v>
       </c>
-      <c r="I5" s="1" t="b">
-        <f aca="false">ISNA(VLOOKUP("ZZZ",Lookup1!A:C,2,FALSE()))</f>
-        <v>1</v>
-      </c>
-      <c r="J5" s="0" t="e">
+      <c r="P5" s="1" t="b">
+        <f aca="false">ISERROR(A5)</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="0" t="n">
+        <f aca="false">TYPE(A5)</f>
+        <v>1</v>
+      </c>
+      <c r="R5" s="0" t="n">
+        <f aca="false">TYPE(B5)</f>
+        <v>2</v>
+      </c>
+      <c r="S5" s="0" t="n">
+        <f aca="false">TYPE(C5)</f>
+        <v>8</v>
+      </c>
+      <c r="T5" s="0" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
-      </c>
-      <c r="K5" s="0" t="n">
-        <f aca="false">TYPE(A5)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="n">
-        <v>-5</v>
+        <v>3.14</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="D6" s="1" t="b">
+      <c r="E6" s="1" t="b">
+        <f aca="false">ISBLANK(A6)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="b">
+        <f aca="false">ISBLANK(D6)</f>
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="b">
         <f aca="false">ISNUMBER(A6)</f>
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="b">
+      <c r="H6" s="1" t="b">
+        <f aca="false">ISNUMBER(B6)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="1" t="b">
         <f aca="false">ISTEXT(B6)</f>
         <v>1</v>
       </c>
-      <c r="F6" s="1" t="b">
+      <c r="J6" s="1" t="b">
+        <f aca="false">ISTEXT(A6)</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="b">
         <f aca="false">ISLOGICAL(C6)</f>
         <v>1</v>
       </c>
-      <c r="G6" s="1" t="b">
+      <c r="L6" s="1" t="b">
+        <f aca="false">ISLOGICAL(A6)</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="1" t="b">
         <f aca="false">ISNONTEXT(A6)</f>
         <v>1</v>
       </c>
-      <c r="H6" s="1" t="b">
+      <c r="N6" s="1" t="b">
+        <f aca="false">ISNONTEXT(B6)</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="1" t="b">
         <f aca="false">ISERROR(1/0)</f>
         <v>1</v>
       </c>
-      <c r="I6" s="1" t="b">
-        <f aca="false">ISNA(VLOOKUP("ZZZ",Lookup1!A:C,2,FALSE()))</f>
-        <v>1</v>
-      </c>
-      <c r="J6" s="0" t="e">
+      <c r="P6" s="1" t="b">
+        <f aca="false">ISERROR(A6)</f>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="0" t="n">
+        <f aca="false">TYPE(A6)</f>
+        <v>1</v>
+      </c>
+      <c r="R6" s="0" t="n">
+        <f aca="false">TYPE(B6)</f>
+        <v>2</v>
+      </c>
+      <c r="S6" s="0" t="n">
+        <f aca="false">TYPE(C6)</f>
+        <v>8</v>
+      </c>
+      <c r="T6" s="0" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
-      </c>
-      <c r="K6" s="0" t="n">
-        <f aca="false">TYPE(A6)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
-        <v>50</v>
+        <v>999</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="1" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="b">
+        <f aca="false">ISBLANK(A7)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="b">
+        <f aca="false">ISBLANK(D7)</f>
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="b">
         <f aca="false">ISNUMBER(A7)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="1" t="b">
+      <c r="H7" s="1" t="b">
+        <f aca="false">ISNUMBER(B7)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="b">
         <f aca="false">ISTEXT(B7)</f>
         <v>1</v>
       </c>
-      <c r="F7" s="1" t="b">
+      <c r="J7" s="1" t="b">
+        <f aca="false">ISTEXT(A7)</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="1" t="b">
         <f aca="false">ISLOGICAL(C7)</f>
         <v>1</v>
       </c>
-      <c r="G7" s="1" t="b">
+      <c r="L7" s="1" t="b">
+        <f aca="false">ISLOGICAL(A7)</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="1" t="b">
         <f aca="false">ISNONTEXT(A7)</f>
         <v>1</v>
       </c>
-      <c r="H7" s="1" t="b">
+      <c r="N7" s="1" t="b">
+        <f aca="false">ISNONTEXT(B7)</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="1" t="b">
         <f aca="false">ISERROR(1/0)</f>
         <v>1</v>
       </c>
-      <c r="I7" s="1" t="b">
-        <f aca="false">ISNA(VLOOKUP("ZZZ",Lookup1!A:C,2,FALSE()))</f>
-        <v>1</v>
-      </c>
-      <c r="J7" s="0" t="e">
+      <c r="P7" s="1" t="b">
+        <f aca="false">ISERROR(A7)</f>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="0" t="n">
+        <f aca="false">TYPE(A7)</f>
+        <v>1</v>
+      </c>
+      <c r="R7" s="0" t="n">
+        <f aca="false">TYPE(B7)</f>
+        <v>2</v>
+      </c>
+      <c r="S7" s="0" t="n">
+        <f aca="false">TYPE(C7)</f>
+        <v>8</v>
+      </c>
+      <c r="T7" s="0" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
-      </c>
-      <c r="K7" s="0" t="n">
-        <f aca="false">TYPE(A7)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
-        <v>75</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="1" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D8" s="1" t="b">
-        <f aca="false">ISNUMBER(A8)</f>
-        <v>1</v>
-      </c>
-      <c r="E8" s="1" t="b">
-        <f aca="false">ISTEXT(B8)</f>
-        <v>1</v>
-      </c>
-      <c r="F8" s="1" t="b">
-        <f aca="false">ISLOGICAL(C8)</f>
-        <v>1</v>
-      </c>
-      <c r="G8" s="1" t="b">
-        <f aca="false">ISNONTEXT(A8)</f>
-        <v>1</v>
-      </c>
-      <c r="H8" s="1" t="b">
-        <f aca="false">ISERROR(1/0)</f>
-        <v>1</v>
-      </c>
-      <c r="I8" s="1" t="b">
-        <f aca="false">ISNA(VLOOKUP("ZZZ",Lookup1!A:C,2,FALSE()))</f>
-        <v>1</v>
-      </c>
-      <c r="J8" s="0" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K8" s="0" t="n">
-        <f aca="false">TYPE(A8)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="1" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="1" t="b">
-        <f aca="false">ISNUMBER(A9)</f>
-        <v>1</v>
-      </c>
-      <c r="E9" s="1" t="b">
-        <f aca="false">ISTEXT(B9)</f>
-        <v>1</v>
-      </c>
-      <c r="F9" s="1" t="b">
-        <f aca="false">ISLOGICAL(C9)</f>
-        <v>1</v>
-      </c>
-      <c r="G9" s="1" t="b">
-        <f aca="false">ISNONTEXT(A9)</f>
-        <v>1</v>
-      </c>
-      <c r="H9" s="1" t="b">
-        <f aca="false">ISERROR(1/0)</f>
-        <v>1</v>
-      </c>
-      <c r="I9" s="1" t="b">
-        <f aca="false">ISNA(VLOOKUP("ZZZ",Lookup1!A:C,2,FALSE()))</f>
-        <v>1</v>
-      </c>
-      <c r="J9" s="0" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K9" s="0" t="n">
-        <f aca="false">TYPE(A9)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
-        <v>999</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="1" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D10" s="1" t="b">
-        <f aca="false">ISNUMBER(A10)</f>
-        <v>1</v>
-      </c>
-      <c r="E10" s="1" t="b">
-        <f aca="false">ISTEXT(B10)</f>
-        <v>1</v>
-      </c>
-      <c r="F10" s="1" t="b">
-        <f aca="false">ISLOGICAL(C10)</f>
-        <v>1</v>
-      </c>
-      <c r="G10" s="1" t="b">
-        <f aca="false">ISNONTEXT(A10)</f>
-        <v>1</v>
-      </c>
-      <c r="H10" s="1" t="b">
-        <f aca="false">ISERROR(1/0)</f>
-        <v>1</v>
-      </c>
-      <c r="I10" s="1" t="b">
-        <f aca="false">ISNA(VLOOKUP("ZZZ",Lookup1!A:C,2,FALSE()))</f>
-        <v>1</v>
-      </c>
-      <c r="J10" s="0" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K10" s="0" t="n">
-        <f aca="false">TYPE(A10)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
-        <v>42</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="1" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D11" s="1" t="b">
-        <f aca="false">ISNUMBER(A11)</f>
-        <v>1</v>
-      </c>
-      <c r="E11" s="1" t="b">
-        <f aca="false">ISTEXT(B11)</f>
-        <v>1</v>
-      </c>
-      <c r="F11" s="1" t="b">
-        <f aca="false">ISLOGICAL(C11)</f>
-        <v>1</v>
-      </c>
-      <c r="G11" s="1" t="b">
-        <f aca="false">ISNONTEXT(A11)</f>
-        <v>1</v>
-      </c>
-      <c r="H11" s="1" t="b">
-        <f aca="false">ISERROR(1/0)</f>
-        <v>1</v>
-      </c>
-      <c r="I11" s="1" t="b">
-        <f aca="false">ISNA(VLOOKUP("ZZZ",Lookup1!A:C,2,FALSE()))</f>
-        <v>1</v>
-      </c>
-      <c r="J11" s="0" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K11" s="0" t="n">
-        <f aca="false">TYPE(A11)</f>
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="0" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="0" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>75</v>
       </c>
     </row>
   </sheetData>
